--- a/dosyalar/excel-klinigi/ExcelKlinigi_KILER_Erzak_Takibi.xlsx
+++ b/dosyalar/excel-klinigi/ExcelKlinigi_KILER_Erzak_Takibi.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">Tek tarih</t>
   </si>
   <si>
-    <t xml:space="preserve">Aynı üründen farklı tarihli paketler varsa en yakın tarihi yaz ya da ayrı satır aç.</t>
+    <t xml:space="preserve">Aynı üründen farklı tarihli paketler varsa en yakın tarihi yaz; her ürün adı bir kez girilir.</t>
   </si>
   <si>
     <t xml:space="preserve">Kapasite</t>
@@ -992,7 +992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
         <v>11</v>
       </c>
